--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="243">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Entrée Résultat d'examen de laboratoire</t>
+    <t>Résultats d'examen de biologie médicale</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -420,6 +420,9 @@
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'observation</t>
   </si>
   <si>
     <t>Statut</t>
@@ -446,6 +449,325 @@
   </si>
   <si>
     <t>fr-lm-entry.header.language</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.directSubject[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-procedure</t>
+  </si>
+  <si>
+    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.directSubject[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.observationDate[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Date de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.observationDate[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.type</t>
+  </si>
+  <si>
+    <t>Type d'observation</t>
+  </si>
+  <si>
+    <t>LOINC (2.16.840.1.113883.6.1) ou autre</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.type</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.originalName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Nom de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.originalName</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.method</t>
+  </si>
+  <si>
+    <t>Méthode utilisée pour l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.method</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-specimen
+</t>
+  </si>
+  <si>
+    <t>Prélèvement</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.specimen</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-service-request
+</t>
+  </si>
+  <si>
+    <t>Demande d'examen correspondante</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.order</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
+  </si>
+  <si>
+    <t>Localisation anatomique</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.bodySite</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.result</t>
+  </si>
+  <si>
+    <t>Résultats d'examen</t>
+  </si>
+  <si>
+    <t>Valeur de l'observation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.result</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.result.Value[x]</t>
+  </si>
+  <si>
+    <t>string
+QuantityRangeRatioCodeableConceptboolean</t>
+  </si>
+  <si>
+    <t>Valeur de l'observation. Le type de donnée doit être adapté au type d'observation.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.result.Value[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange</t>
+  </si>
+  <si>
+    <t>Intervalle de référence. Plusieurs intervalles de référence, de types différents, peuvent être fournis.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Limite inférieure de l'intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): UCUM for units</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.low</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.high</t>
+  </si>
+  <si>
+    <t>Limite supérieure de l'intervalle</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.high</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.normalValue</t>
+  </si>
+  <si>
+    <t>Valeur normale si pertinente pour l'intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): SNOMED CT</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.normalValue</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.type</t>
+  </si>
+  <si>
+    <t>Type d'intervalle de référence</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 Observation Reference Range Meaning Codes</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.type</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>Population concernée pour cet intervalle</t>
+  </si>
+  <si>
+    <t>(preferred): SNOMED CT, HL7 v3-Race</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Tranche d'âge pour cet intervalle</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.age</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.referenceRange.text</t>
+  </si>
+  <si>
+    <t>Texte libre</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.referenceRange.text</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.interpretation</t>
+  </si>
+  <si>
+    <t>Interprétation</t>
+  </si>
+  <si>
+    <t>(preferred): HL7 Observation Interpretation Codes</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.interpretation</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.note</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.note</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.component</t>
+  </si>
+  <si>
+    <t>Composant dans le cas d'une observation composée de plusieurs sous-observations</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.component</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.derivedFrom[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-laboratory-observationhttps://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-imaging-study</t>
+  </si>
+  <si>
+    <t>Référence de la resource à partir de laquelle l'observation a été faite. Par exemple, une image échographique à partir de laquelle une mesure fœtale est réalisée.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.derivedFrom[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.hasMember[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-laboratory-observation
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-observation</t>
+  </si>
+  <si>
+    <t>Cette observation est un groupe d'observations (par exemple, une batterie de tests, un ensemble de mesures de signes vitaux).</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.hasMember[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.triggeredBy[x]</t>
+  </si>
+  <si>
+    <t>Référence à l'observation ayant déclenché la réalisation de cette observation.</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.testKit</t>
+  </si>
+  <si>
+    <t>Test Kit utilisé pour la réalisation de l'observation.</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.calibrator</t>
+  </si>
+  <si>
+    <t>Identifiant du calibrateur utilisé pour la réalisation de l'observation.</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.accreditationStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Statut d'accréditation du laboratoire pour l'observation.</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.previousResults</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-laboratory-observation
+</t>
+  </si>
+  <si>
+    <t>Résultats précédents de la même observation</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.pointOfCareTest</t>
+  </si>
+  <si>
+    <t>Indique si l'observation est un test de point de soins ou non.</t>
   </si>
 </sst>
 </file>
@@ -747,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.51171875" customWidth="true" bestFit="true"/>
@@ -760,7 +1082,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -774,8 +1096,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="50.2578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -2410,7 +2732,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2431,7 +2753,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2482,7 +2804,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>74</v>
@@ -2499,10 +2821,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2528,10 +2850,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2582,7 +2904,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2599,10 +2921,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2628,10 +2950,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2682,7 +3004,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2694,6 +3016,2906 @@
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
